--- a/Tyr_Mars_Rover/Mars_Rover_Parts_List.xlsx
+++ b/Tyr_Mars_Rover/Mars_Rover_Parts_List.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\_WNCC\GitHub\WNCCNASA\Mars_Rover\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\_WNCC\NASA\Tyr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EEA73A-5C39-4E1C-8F02-F95BF546DA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFD2262-C555-4EE4-85E2-D95B01B281B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29510" yWindow="3590" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Qty</t>
   </si>
@@ -54,6 +54,69 @@
   </si>
   <si>
     <t>Parts List</t>
+  </si>
+  <si>
+    <t>Wires to motors</t>
+  </si>
+  <si>
+    <t>520mm</t>
+  </si>
+  <si>
+    <t>Screws and nut for each motor</t>
+  </si>
+  <si>
+    <t>M3x35</t>
+  </si>
+  <si>
+    <t>M3x8</t>
+  </si>
+  <si>
+    <t>M3x16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M6 </t>
+  </si>
+  <si>
+    <t>Locknut</t>
+  </si>
+  <si>
+    <t>M3x40</t>
+  </si>
+  <si>
+    <t>M3x32</t>
+  </si>
+  <si>
+    <t>M3x18</t>
+  </si>
+  <si>
+    <t>M3x12</t>
+  </si>
+  <si>
+    <t>M8 Nut for threaded rod</t>
+  </si>
+  <si>
+    <t>M2x8</t>
+  </si>
+  <si>
+    <t>M6x45</t>
+  </si>
+  <si>
+    <t>Need</t>
+  </si>
+  <si>
+    <t>M3x10</t>
+  </si>
+  <si>
+    <t>3mm magnets glued in</t>
+  </si>
+  <si>
+    <t>285mm M8 Threaded Rod</t>
+  </si>
+  <si>
+    <t>30 or 25 on hand</t>
+  </si>
+  <si>
+    <t>16 or 20 on hand</t>
   </si>
 </sst>
 </file>
@@ -391,22 +454,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -417,15 +480,156 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
         <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
